--- a/Models/Птицы/results/Птица - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Птицы/results/Птица - Результаты прогнозов SARIMA.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -507,22 +507,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>751.48</v>
+        <v>1560.23</v>
       </c>
       <c r="G2" t="n">
-        <v>593.33</v>
+        <v>1519.52</v>
       </c>
       <c r="H2" t="n">
-        <v>5.69</v>
+        <v>14.92</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[8994.06, 8997.39, 9809.41]</t>
+          <t>[12055.2, 11745.27, 11363.15]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[8963.23, 9586.12, 10969.85]</t>
+          <t>[10080.07, 10273.59, 10251.41]</t>
         </is>
       </c>
     </row>
@@ -534,41 +534,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(3, 1, 0)</t>
+          <t>(3, 1, 2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>828.4299999999999</v>
+        <v>826.83</v>
       </c>
       <c r="G3" t="n">
-        <v>772.8</v>
+        <v>675.33</v>
       </c>
       <c r="H3" t="n">
-        <v>7.33</v>
+        <v>7.37</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[8969.3, 9779.4, 10383.83]</t>
+          <t>[10097.2, 9719.86, 9983.27]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[9586.12, 10969.85, 10894.97]</t>
+          <t>[10273.59, 10251.41, 8665.21]</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(3, 1, 0)</t>
+          <t>(3, 1, 2)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>569.84</v>
+        <v>1139.37</v>
       </c>
       <c r="G4" t="n">
-        <v>432.16</v>
+        <v>868.74</v>
       </c>
       <c r="H4" t="n">
-        <v>4.01</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[10035.51, 10847.31, 10553.45]</t>
+          <t>[9770.54, 10565.95, 11663.35]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[10969.85, 10894.97, 10238.97]</t>
+          <t>[10251.41, 8665.21, 11438.74]</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -641,26 +641,26 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1161</v>
+        <v>1519.82</v>
       </c>
       <c r="G5" t="n">
-        <v>902.61</v>
+        <v>1398.51</v>
       </c>
       <c r="H5" t="n">
-        <v>7.61</v>
+        <v>15.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[11015.8, 10948.1, 10814.61]</t>
+          <t>[10767.35, 12085.82, 10006.61]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[10894.97, 10238.97, 12692.46]</t>
+          <t>[8665.21, 11438.74, 8560.3]</t>
         </is>
       </c>
     </row>
@@ -672,41 +672,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 1, 2)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1054.11</v>
+        <v>1283.4</v>
       </c>
       <c r="G6" t="n">
-        <v>848.4299999999999</v>
+        <v>881.59</v>
       </c>
       <c r="H6" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[10377.68, 11031.78, 11125.06]</t>
+          <t>[11039.41, 8619.8, 10365.56]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[10238.97, 12692.46, 10379.17]</t>
+          <t>[11438.74, 8560.3, 12551.51]</t>
         </is>
       </c>
     </row>
@@ -718,17 +718,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(3, 1, 2)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1272.51</v>
+        <v>1714.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1177.22</v>
+        <v>1356.66</v>
       </c>
       <c r="H7" t="n">
-        <v>10.42</v>
+        <v>10.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[10925.0, 10963.17, 11260.29]</t>
+          <t>[8621.92, 9920.44, 11008.0]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[12692.46, 10379.17, 10080.07]</t>
+          <t>[8560.3, 12551.51, 12385.3]</t>
         </is>
       </c>
     </row>
@@ -764,41 +764,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(3, 1, 0)</t>
+          <t>(2, 1, 3)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1998.02</v>
+        <v>1867.03</v>
       </c>
       <c r="G8" t="n">
-        <v>1895.22</v>
+        <v>1835.1</v>
       </c>
       <c r="H8" t="n">
-        <v>18.57</v>
+        <v>14.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[11385.75, 12509.32, 12523.44]</t>
+          <t>[10607.55, 11015.04, 10824.81]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[10379.17, 10080.07, 10273.59]</t>
+          <t>[12551.51, 12385.3, 13015.9]</t>
         </is>
       </c>
     </row>
@@ -810,41 +810,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(3, 1, 0)</t>
+          <t>(2, 1, 3)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1560.23</v>
+        <v>1255.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1519.52</v>
+        <v>1085.9</v>
       </c>
       <c r="H9" t="n">
-        <v>14.92</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[12055.2, 11745.27, 11363.15]</t>
+          <t>[11873.87, 12233.43, 12572.8]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[10080.07, 10273.59, 10251.41]</t>
+          <t>[12385.3, 13015.9, 10609.0]</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -871,26 +871,26 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>826.83</v>
+        <v>2167.27</v>
       </c>
       <c r="G10" t="n">
-        <v>675.33</v>
+        <v>1856.73</v>
       </c>
       <c r="H10" t="n">
-        <v>7.37</v>
+        <v>17.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[10097.2, 9719.86, 9983.27]</t>
+          <t>[12734.39, 13137.25, 13169.02]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[10273.59, 10251.41, 8665.21]</t>
+          <t>[13015.9, 10609.0, 10408.6]</t>
         </is>
       </c>
     </row>
@@ -902,41 +902,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(3, 1, 2)</t>
+          <t>(2, 1, 3)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1139.37</v>
+        <v>2162.84</v>
       </c>
       <c r="G11" t="n">
-        <v>868.74</v>
+        <v>2135.45</v>
       </c>
       <c r="H11" t="n">
-        <v>9.529999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[9770.54, 10565.95, 11663.35]</t>
+          <t>[13041.61, 12727.68, 12294.35]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[10251.41, 8665.21, 11438.74]</t>
+          <t>[10609.0, 10408.6, 10639.7]</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,22 +967,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.4</v>
+        <v>37.23</v>
       </c>
       <c r="G12" t="n">
-        <v>30.51</v>
+        <v>28.98</v>
       </c>
       <c r="H12" t="n">
-        <v>39.16</v>
+        <v>1276.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[65.39, 45.68, 2.77]</t>
+          <t>[73.33, 62.24, 86.36]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[64.3, 56.5, 82.4]</t>
+          <t>[68.4, 1.6, 65.0]</t>
         </is>
       </c>
     </row>
@@ -994,17 +994,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.19</v>
+        <v>50.09</v>
       </c>
       <c r="G13" t="n">
-        <v>37.74</v>
+        <v>46.56</v>
       </c>
       <c r="H13" t="n">
-        <v>52.75</v>
+        <v>1273.96</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[45.36, 2.78, 31.13]</t>
+          <t>[60.68, 85.44, 121.45]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[56.5, 82.4, 53.6]</t>
+          <t>[1.6, 65.0, 61.3]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>47.57</v>
+        <v>86.52</v>
       </c>
       <c r="G14" t="n">
-        <v>35.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>49.43</v>
+        <v>53.73</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[2.98, 32.07, 41.34]</t>
+          <t>[16.7, 41.94, 113.66]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[82.4, 53.6, 37.0]</t>
+          <t>[65.0, 61.3, 254.2]</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>21.25</v>
+        <v>72.16</v>
       </c>
       <c r="G15" t="n">
-        <v>20.31</v>
+        <v>46.39</v>
       </c>
       <c r="H15" t="n">
-        <v>44.92</v>
+        <v>25.27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[70.31, 52.13, 17.31]</t>
+          <t>[63.48, 129.88, 41.63]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[53.6, 37.0, 46.4]</t>
+          <t>[61.3, 254.2, 54.3]</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>30.71</v>
+        <v>73.14</v>
       </c>
       <c r="G16" t="n">
-        <v>27.57</v>
+        <v>46.35</v>
       </c>
       <c r="H16" t="n">
-        <v>57.61</v>
+        <v>24.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[46.98, 16.55, 9.72]</t>
+          <t>[128.19, 41.31, 30.46]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[37.0, 46.4, 52.6]</t>
+          <t>[254.2, 54.3, 30.5]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38.24</v>
+        <v>4.77</v>
       </c>
       <c r="G17" t="n">
-        <v>37.92</v>
+        <v>4.35</v>
       </c>
       <c r="H17" t="n">
-        <v>68.94</v>
+        <v>17.84</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[15.25, 9.52, 28.89]</t>
+          <t>[50.64, 32.88, 10.99]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[46.4, 52.6, 68.4]</t>
+          <t>[54.3, 30.5, 18.0]</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>34.69</v>
+        <v>12.92</v>
       </c>
       <c r="G18" t="n">
-        <v>34.46</v>
+        <v>10.32</v>
       </c>
       <c r="H18" t="n">
-        <v>649.74</v>
+        <v>30.49</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[13.57, 33.24, 30.78]</t>
+          <t>[33.49, 11.11, 27.51]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[52.6, 68.4, 1.6]</t>
+          <t>[30.5, 18.0, 48.6]</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>37.23</v>
+        <v>13.46</v>
       </c>
       <c r="G19" t="n">
-        <v>28.98</v>
+        <v>11.52</v>
       </c>
       <c r="H19" t="n">
-        <v>1276.65</v>
+        <v>36.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[73.33, 62.24, 86.36]</t>
+          <t>[10.94, 27.26, 30.06]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[68.4, 1.6, 65.0]</t>
+          <t>[18.0, 48.6, 23.9]</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50.09</v>
+        <v>24.61</v>
       </c>
       <c r="G20" t="n">
-        <v>46.56</v>
+        <v>21.01</v>
       </c>
       <c r="H20" t="n">
-        <v>1273.96</v>
+        <v>46.41</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[60.68, 85.44, 121.45]</t>
+          <t>[30.82, 31.07, 14.33]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[1.6, 65.0, 61.3]</t>
+          <t>[48.6, 23.9, 52.4]</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>86.52</v>
+        <v>36.13</v>
       </c>
       <c r="G21" t="n">
-        <v>69.40000000000001</v>
+        <v>32.59</v>
       </c>
       <c r="H21" t="n">
-        <v>53.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[16.7, 41.94, 113.66]</t>
+          <t>[35.44, 15.05, 11.73]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[65.0, 61.3, 254.2]</t>
+          <t>[23.9, 52.4, 60.6]</t>
         </is>
       </c>
     </row>
@@ -1408,41 +1408,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>942.99</v>
+        <v>1491.29</v>
       </c>
       <c r="G22" t="n">
-        <v>755.9</v>
+        <v>1322.57</v>
       </c>
       <c r="H22" t="n">
-        <v>6.31</v>
+        <v>11.71</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[11478.69, 10441.92, 10798.41]</t>
+          <t>[10612.83, 9278.09, 9699.72]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[11949.02, 10187.92, 12341.77]</t>
+          <t>[11018.07, 10774.72, 11765.56]</t>
         </is>
       </c>
     </row>
@@ -1454,41 +1454,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>787.1799999999999</v>
+        <v>2554.52</v>
       </c>
       <c r="G23" t="n">
-        <v>567.16</v>
+        <v>2348.73</v>
       </c>
       <c r="H23" t="n">
-        <v>4.82</v>
+        <v>19.66</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[10570.46, 11033.15, 11349.63]</t>
+          <t>[9432.49, 9781.77, 8826.31]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[10187.92, 12341.77, 11359.95]</t>
+          <t>[10774.72, 11765.56, 12546.48]</t>
         </is>
       </c>
     </row>
@@ -1500,41 +1500,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>943.12</v>
+        <v>2446.79</v>
       </c>
       <c r="G24" t="n">
-        <v>752.76</v>
+        <v>2187.75</v>
       </c>
       <c r="H24" t="n">
-        <v>6.26</v>
+        <v>17.84</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[10863.16, 11268.61, 10775.88]</t>
+          <t>[9921.32, 8878.43, 11156.98]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[12341.77, 11359.95, 11464.21]</t>
+          <t>[11765.56, 12546.48, 12207.96]</t>
         </is>
       </c>
     </row>
@@ -1546,41 +1546,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>483.64</v>
+        <v>1678.39</v>
       </c>
       <c r="G25" t="n">
-        <v>467.14</v>
+        <v>1182.21</v>
       </c>
       <c r="H25" t="n">
-        <v>4.14</v>
+        <v>9.48</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[11986.08, 11144.16, 11547.18]</t>
+          <t>[9694.88, 11663.16, 11873.08]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[11359.95, 11464.21, 11091.93]</t>
+          <t>[12546.48, 12207.96, 12023.33]</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1607,26 +1607,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1054.1</v>
+        <v>792.71</v>
       </c>
       <c r="G26" t="n">
-        <v>867.13</v>
+        <v>690.17</v>
       </c>
       <c r="H26" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[10834.72, 11373.26, 10621.39]</t>
+          <t>[13334.07, 12788.01, 11000.8]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[11464.21, 11091.93, 12311.95]</t>
+          <t>[12207.96, 12023.33, 10821.1]</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1653,26 +1653,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>935.91</v>
+        <v>676.73</v>
       </c>
       <c r="G27" t="n">
-        <v>917.01</v>
+        <v>431.07</v>
       </c>
       <c r="H27" t="n">
-        <v>7.94</v>
+        <v>3.42</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[11784.91, 11160.93, 10111.05]</t>
+          <t>[12098.09, 10870.85, 11584.27]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[11091.93, 12311.95, 11018.07]</t>
+          <t>[12023.33, 10821.1, 12752.96]</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1699,26 +1699,26 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1546.82</v>
+        <v>1304.07</v>
       </c>
       <c r="G28" t="n">
-        <v>1518.27</v>
+        <v>1037.01</v>
       </c>
       <c r="H28" t="n">
-        <v>13.33</v>
+        <v>7.91</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[10544.48, 9915.42, 9090.04]</t>
+          <t>[10815.89, 11573.37, 11420.61]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[12311.95, 11018.07, 10774.72]</t>
+          <t>[10821.1, 12752.96, 13346.82]</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1491.29</v>
+        <v>1334.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1322.57</v>
+        <v>1207.98</v>
       </c>
       <c r="H29" t="n">
-        <v>11.71</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[10612.83, 9278.09, 9699.72]</t>
+          <t>[11573.92, 11429.61, 11091.53]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[11018.07, 10774.72, 11765.56]</t>
+          <t>[12752.96, 13346.82, 11619.21]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1795,22 +1795,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2554.52</v>
+        <v>1205.38</v>
       </c>
       <c r="G30" t="n">
-        <v>2348.73</v>
+        <v>1054.77</v>
       </c>
       <c r="H30" t="n">
-        <v>19.66</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[9432.49, 9781.77, 8826.31]</t>
+          <t>[11989.34, 11380.55, 12073.31]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[10774.72, 11765.56, 12546.48]</t>
+          <t>[13346.82, 11619.21, 10505.14]</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1841,22 +1841,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2446.79</v>
+        <v>860.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2187.75</v>
+        <v>703.5599999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>17.84</v>
+        <v>6.56</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[9921.32, 8878.43, 11156.98]</t>
+          <t>[11952.84, 11908.94, 10471.0]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[11765.56, 12546.48, 12207.96]</t>
+          <t>[11619.21, 10505.14, 10844.25]</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1893,11 +1893,11 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.502129215490562e+19</v>
+        <v>4.582818746858597e+18</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.781203523240935e+19</v>
+        <v>9.255261611742446e+18</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1979,22 +1979,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H34" t="n">
-        <v>2.422152083121981e+22</v>
+        <v>3.410634518981203e+18</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.31]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="H35" t="n">
-        <v>8.190005870450978e+21</v>
+        <v>5.728806219726925e+17</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2071,22 +2071,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.02</v>
+        <v>0.35</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="H36" t="n">
-        <v>2.561956173794257e+21</v>
+        <v>2.055783778651128e+16</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[0.03, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2123,11 +2123,11 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5.708612469482005e+17</v>
+        <v>1.225060950461276e+19</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2169,11 +2169,11 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>8.615029272853883e+17</v>
+        <v>5.384052310435165e+18</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2215,11 +2215,11 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>4.582818746858597e+18</v>
+        <v>1.84791580516596e+19</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2261,11 +2261,11 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>9.255261611742446e+18</v>
+        <v>6.272300831556545e+18</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2297,26 +2297,26 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3.410634518981203e+18</v>
+        <v>4.41215692777343e+18</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>[0.0, -0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2347,22 +2347,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1216.92</v>
+        <v>329.52</v>
       </c>
       <c r="G42" t="n">
-        <v>1194.91</v>
+        <v>302.72</v>
       </c>
       <c r="H42" t="n">
-        <v>18.82</v>
+        <v>5.03</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[5240.5, 4936.08, 5164.74]</t>
+          <t>[5940.29, 5831.3, 6643.95]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[6353.35, 5898.97, 6673.73]</t>
+          <t>[6144.41, 5613.89, 6157.31]</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2393,22 +2393,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>659.38</v>
+        <v>656.37</v>
       </c>
       <c r="G43" t="n">
-        <v>579.51</v>
+        <v>613.97</v>
       </c>
       <c r="H43" t="n">
-        <v>9.029999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[5631.79, 5663.71, 5756.55]</t>
+          <t>[5959.29, 6742.15, 6955.45]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[5898.97, 6673.73, 6217.87]</t>
+          <t>[5613.89, 6157.31, 6043.79]</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2439,22 +2439,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>739.95</v>
+        <v>576.95</v>
       </c>
       <c r="G44" t="n">
-        <v>695.0700000000001</v>
+        <v>549.91</v>
       </c>
       <c r="H44" t="n">
-        <v>10.35</v>
+        <v>9.09</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[5840.39, 5878.77, 6043.68]</t>
+          <t>[6464.28, 6753.1, 6631.64]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[6673.73, 6217.87, 6956.45]</t>
+          <t>[6157.31, 6043.79, 5998.19]</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2485,22 +2485,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>495.25</v>
+        <v>399.5</v>
       </c>
       <c r="G45" t="n">
-        <v>455.92</v>
+        <v>330.32</v>
       </c>
       <c r="H45" t="n">
-        <v>7.01</v>
+        <v>5.48</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[6410.01, 6431.23, 5613.89]</t>
+          <t>[6533.86, 6486.52, 6364.39]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[6217.87, 6956.45, 6264.3]</t>
+          <t>[6043.79, 5998.19, 6376.96]</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>640.95</v>
+        <v>218.43</v>
       </c>
       <c r="G46" t="n">
-        <v>637.5700000000001</v>
+        <v>214.35</v>
       </c>
       <c r="H46" t="n">
-        <v>10.05</v>
+        <v>3.6</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[6304.88, 5554.16, 5275.36]</t>
+          <t>[6153.26, 6137.27, 5823.09]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[6956.45, 6264.3, 5826.35]</t>
+          <t>[5998.19, 6376.96, 5574.81]</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>312.22</v>
+        <v>337.18</v>
       </c>
       <c r="G47" t="n">
-        <v>306.19</v>
+        <v>320.08</v>
       </c>
       <c r="H47" t="n">
-        <v>5.03</v>
+        <v>5.12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[5988.91, 5574.59, 5752.98]</t>
+          <t>[6032.29, 5754.52, 6033.47]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[6264.3, 5826.35, 6144.41]</t>
+          <t>[6376.96, 5574.81, 6469.33]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>182.18</v>
+        <v>284.29</v>
       </c>
       <c r="G48" t="n">
-        <v>162.44</v>
+        <v>255.59</v>
       </c>
       <c r="H48" t="n">
-        <v>2.76</v>
+        <v>4.28</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[5778.53, 5905.96, 5814.94]</t>
+          <t>[5975.53, 6200.0, 6389.38]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[5826.35, 6144.41, 5613.89]</t>
+          <t>[5574.81, 6469.33, 6486.09]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>329.52</v>
+        <v>385.08</v>
       </c>
       <c r="G49" t="n">
-        <v>302.72</v>
+        <v>357.53</v>
       </c>
       <c r="H49" t="n">
-        <v>5.03</v>
+        <v>5.57</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[5940.29, 5831.3, 6643.95]</t>
+          <t>[5914.63, 6187.93, 6441.55]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[6144.41, 5613.89, 6157.31]</t>
+          <t>[6469.33, 6486.09, 6221.83]</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>656.37</v>
+        <v>552.67</v>
       </c>
       <c r="G50" t="n">
-        <v>613.97</v>
+        <v>461.72</v>
       </c>
       <c r="H50" t="n">
-        <v>10.25</v>
+        <v>7.51</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[5959.29, 6742.15, 6955.45]</t>
+          <t>[6559.03, 6719.73, 5255.0]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[5613.89, 6157.31, 6043.79]</t>
+          <t>[6486.09, 6221.83, 6069.31]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>576.95</v>
+        <v>946.97</v>
       </c>
       <c r="G51" t="n">
-        <v>549.91</v>
+        <v>874.48</v>
       </c>
       <c r="H51" t="n">
-        <v>9.09</v>
+        <v>14.21</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[6464.28, 6753.1, 6631.64]</t>
+          <t>[6669.87, 5229.97, 4850.63]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[6157.31, 6043.79, 5998.19]</t>
+          <t>[6221.83, 6069.31, 6186.68]</t>
         </is>
       </c>
     </row>
@@ -2788,17 +2788,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(4, 0, 0)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2807,22 +2807,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>98.33</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0.2, 0.1, 0.1]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2834,17 +2834,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(4, 0, 0)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2853,17 +2853,17 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H53" t="n">
-        <v>99.98999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.01, 0.0, 0.03]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(4, 0, 3)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2899,17 +2899,17 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.1</v>
+        <v>1.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H54" t="n">
-        <v>99.68000000000001</v>
+        <v>795.72</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.03, 2.34, 0.03]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(4, 0, 3)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2945,17 +2945,17 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.1</v>
+        <v>2.52</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
       <c r="H55" t="n">
-        <v>99.3</v>
+        <v>1942.78</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[4.08, 0.04, 1.89]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2972,17 +2972,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(4, 0, 4)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2991,17 +2991,17 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.1</v>
+        <v>3.63</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1</v>
+        <v>2.79</v>
       </c>
       <c r="H56" t="n">
-        <v>98.39</v>
+        <v>2794.75</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.03, 5.83, 2.69]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(4, 0, 0)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3037,17 +3037,17 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.08</v>
+        <v>5.55</v>
       </c>
       <c r="G57" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="H57" t="n">
-        <v>68.91</v>
+        <v>4898.84</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[0.01, 0.12, 0.0]</t>
+          <t>[8.68, 3.46, 2.85]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3064,17 +3064,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(4, 0, 0)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3083,17 +3083,17 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="G58" t="n">
-        <v>0.14</v>
+        <v>0.58</v>
       </c>
       <c r="H58" t="n">
-        <v>139.11</v>
+        <v>582.28</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[0.32, 0.0, 0.0]</t>
+          <t>[0.57, 0.78, 0.7]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3110,36 +3110,36 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(4, 0, 0)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H59" t="n">
-        <v>98.33</v>
+        <v>128.21</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.45, 0.11, 0.07]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(4, 0, 0)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3175,17 +3175,17 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G60" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H60" t="n">
-        <v>86.43000000000001</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0.01, 0.0, 0.03]</t>
+          <t>[0.08, 0.31, 0.1]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3221,17 +3221,17 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.29</v>
+        <v>11.31</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8</v>
+        <v>6.61</v>
       </c>
       <c r="H61" t="n">
-        <v>795.72</v>
+        <v>6608.44</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0.03, 2.34, 0.03]</t>
+          <t>[0.34, 0.11, 19.68]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3248,22 +3248,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3273,11 +3273,11 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.105902104097685e+17</v>
+        <v>9.053000198497962e+17</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3319,11 +3319,11 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>4.73862727012554e+16</v>
+        <v>1.092582253639377e+17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3359,22 +3359,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>9.03520983268644e+16</v>
+        <v>1.288737898516444e+17</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3386,17 +3386,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.871925080341002e+18</v>
+        <v>1.981866911798795e+17</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>[0.0, 0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3432,17 +3432,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3.125364734769096e+18</v>
+        <v>2.46337440871325e+17</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>[0.0, -0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3503,11 +3503,11 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>3.13774343495103e+20</v>
+        <v>2.022654543304864e+17</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3549,11 +3549,11 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1.922049098542109e+18</v>
+        <v>1.549369179440892e+18</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3570,17 +3570,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3595,11 +3595,11 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>9.053000198497962e+17</v>
+        <v>5.225005279142245e+18</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3616,36 +3616,36 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1.092582253639377e+17</v>
+        <v>1.106842880286723e+21</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.01, 0.0]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3662,22 +3662,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -3687,11 +3687,11 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.288737898516444e+17</v>
+        <v>5.855367897916327e+20</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.01, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3727,22 +3727,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>512.03</v>
+        <v>28.84</v>
       </c>
       <c r="G72" t="n">
-        <v>386.17</v>
+        <v>27.71</v>
       </c>
       <c r="H72" t="n">
-        <v>5494.26</v>
+        <v>714.99</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[141.49, 867.97, 223.34]</t>
+          <t>[40.42, 32.75, 22.46]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[4.6, 6.5, 63.19]</t>
+          <t>[3.3, 4.3, 4.9]</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3773,22 +3773,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>60.56</v>
+        <v>7.44</v>
       </c>
       <c r="G73" t="n">
-        <v>44.07</v>
+        <v>6.77</v>
       </c>
       <c r="H73" t="n">
-        <v>538.95</v>
+        <v>145.69</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[108.98, 42.86, 107.71]</t>
+          <t>[15.38, 9.99, 9.65]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[6.5, 63.19, 117.1]</t>
+          <t>[4.3, 4.9, 5.5]</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>58.49</v>
+        <v>10.49</v>
       </c>
       <c r="G74" t="n">
-        <v>46.47</v>
+        <v>7.15</v>
       </c>
       <c r="H74" t="n">
-        <v>67.92</v>
+        <v>42.54</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[14.24, 28.42, 5.27]</t>
+          <t>[6.94, 6.9, 11.7]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[63.19, 117.1, 3.5]</t>
+          <t>[4.9, 5.5, 29.7]</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3865,22 +3865,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>42.99</v>
+        <v>11.13</v>
       </c>
       <c r="G75" t="n">
-        <v>27.39</v>
+        <v>7.49</v>
       </c>
       <c r="H75" t="n">
-        <v>90.11</v>
+        <v>48.7</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[42.85, 7.84, 7.87]</t>
+          <t>[6.32, 10.6, 1.26]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[117.1, 3.5, 4.3]</t>
+          <t>[5.5, 29.7, 3.8]</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3911,22 +3911,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>34.68</v>
+        <v>11.41</v>
       </c>
       <c r="G76" t="n">
-        <v>23.53</v>
+        <v>8.02</v>
       </c>
       <c r="H76" t="n">
-        <v>121.58</v>
+        <v>56.97</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[9.31, 9.5, 17.13]</t>
+          <t>[10.2, 1.24, 3.3]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[3.5, 4.3, 76.7]</t>
+          <t>[29.7, 3.8, 5.3]</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3957,22 +3957,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>38.03</v>
+        <v>1.66</v>
       </c>
       <c r="G77" t="n">
-        <v>28.65</v>
+        <v>1.58</v>
       </c>
       <c r="H77" t="n">
-        <v>259.24</v>
+        <v>43.83</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[6.86, 14.33, 24.32]</t>
+          <t>[1.55, 4.18, 4.08]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[4.3, 76.7, 3.3]</t>
+          <t>[3.8, 5.3, 2.7]</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4003,22 +4003,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>39.18</v>
+        <v>2.56</v>
       </c>
       <c r="G78" t="n">
-        <v>32.17</v>
+        <v>2.09</v>
       </c>
       <c r="H78" t="n">
-        <v>326.98</v>
+        <v>54.59</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[13.03, 22.28, 18.18]</t>
+          <t>[5.57, 4.79, 8.71]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[76.7, 3.3, 4.3]</t>
+          <t>[5.3, 2.7, 4.8]</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>28.84</v>
+        <v>2.84</v>
       </c>
       <c r="G79" t="n">
-        <v>27.71</v>
+        <v>2.75</v>
       </c>
       <c r="H79" t="n">
-        <v>714.99</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[40.42, 32.75, 22.46]</t>
+          <t>[4.71, 8.52, 1.09]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[3.3, 4.3, 4.9]</t>
+          <t>[2.7, 4.8, 3.6]</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4095,22 +4095,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>7.44</v>
+        <v>2.82</v>
       </c>
       <c r="G80" t="n">
-        <v>6.77</v>
+        <v>2.8</v>
       </c>
       <c r="H80" t="n">
-        <v>145.69</v>
+        <v>67.02</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[15.38, 9.99, 9.65]</t>
+          <t>[7.31, 1.01, 1.0]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[4.3, 4.9, 5.5]</t>
+          <t>[4.8, 3.6, 4.3]</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4141,22 +4141,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>10.49</v>
+        <v>2.71</v>
       </c>
       <c r="G81" t="n">
-        <v>7.15</v>
+        <v>2.65</v>
       </c>
       <c r="H81" t="n">
-        <v>42.54</v>
+        <v>66.84</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[6.94, 6.9, 11.7]</t>
+          <t>[0.98, 0.96, 2.0]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[4.9, 5.5, 29.7]</t>
+          <t>[3.6, 4.3, 4.0]</t>
         </is>
       </c>
     </row>
@@ -4168,17 +4168,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>183.19</v>
+        <v>140.97</v>
       </c>
       <c r="G82" t="n">
-        <v>167.56</v>
+        <v>109.39</v>
       </c>
       <c r="H82" t="n">
-        <v>11.44</v>
+        <v>5.91</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[1354.03, 1563.08, 1485.27]</t>
+          <t>[1637.54, 2047.91, 1953.84]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[1595.03, 1629.31, 1289.81]</t>
+          <t>[1658.56, 1816.86, 2029.92]</t>
         </is>
       </c>
     </row>
@@ -4214,17 +4214,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>227.11</v>
+        <v>421.22</v>
       </c>
       <c r="G83" t="n">
-        <v>208.29</v>
+        <v>332.55</v>
       </c>
       <c r="H83" t="n">
-        <v>13.62</v>
+        <v>17.86</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[1711.04, 1578.15, 2143.34]</t>
+          <t>[2070.57, 1967.13, 2546.67]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[1629.31, 1289.81, 1888.54]</t>
+          <t>[1816.86, 2029.92, 1865.53]</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4279,22 +4279,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>410.45</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>366.38</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>22.54</v>
+        <v>25.97</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[1531.18, 2118.34, 2337.1]</t>
+          <t>[1842.07, 2520.75, 2893.92]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[1289.81, 1888.54, 1709.14]</t>
+          <t>[2029.92, 1865.53, 2167.03]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4325,22 +4325,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>520.55</v>
+        <v>634.4</v>
       </c>
       <c r="G85" t="n">
-        <v>434.27</v>
+        <v>581.96</v>
       </c>
       <c r="H85" t="n">
-        <v>26.73</v>
+        <v>29.02</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[1741.59, 2038.73, 2381.35]</t>
+          <t>[2605.64, 2947.27, 2209.2]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[1888.54, 1709.14, 1555.1]</t>
+          <t>[1865.53, 2167.03, 1983.67]</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4367,26 +4367,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>696.2</v>
+        <v>332.79</v>
       </c>
       <c r="G86" t="n">
-        <v>664.29</v>
+        <v>284.04</v>
       </c>
       <c r="H86" t="n">
-        <v>41.65</v>
+        <v>14.31</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[2237.6, 2513.78, 2066.77]</t>
+          <t>[2590.87, 1944.04, 2206.3]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[1709.14, 1555.1, 1561.05]</t>
+          <t>[2167.03, 1983.67, 1817.65]</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4413,26 +4413,26 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>391.32</v>
+        <v>475.12</v>
       </c>
       <c r="G87" t="n">
-        <v>331.94</v>
+        <v>371.58</v>
       </c>
       <c r="H87" t="n">
-        <v>21.21</v>
+        <v>15.93</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[2147.46, 1879.19, 1743.89]</t>
+          <t>[1863.92, 2025.4, 1808.85]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[1555.1, 1561.05, 1658.56]</t>
+          <t>[1983.67, 1817.65, 2596.07]</t>
         </is>
       </c>
     </row>
@@ -4444,41 +4444,41 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>170.36</v>
+        <v>626.09</v>
       </c>
       <c r="G88" t="n">
-        <v>112.71</v>
+        <v>584.79</v>
       </c>
       <c r="H88" t="n">
-        <v>6.3</v>
+        <v>27.02</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[1549.1, 1625.34, 2109.81]</t>
+          <t>[2086.28, 1846.12, 2704.08]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[1561.05, 1658.56, 1816.86]</t>
+          <t>[1817.65, 2596.07, 1968.29]</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4505,26 +4505,26 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>140.97</v>
+        <v>754.91</v>
       </c>
       <c r="G89" t="n">
-        <v>109.39</v>
+        <v>743</v>
       </c>
       <c r="H89" t="n">
-        <v>5.91</v>
+        <v>34.22</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[1637.54, 2047.91, 1953.84]</t>
+          <t>[1689.96, 2547.2, 2683.62]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[1658.56, 1816.86, 2029.92]</t>
+          <t>[2596.07, 1968.29, 1939.64]</t>
         </is>
       </c>
     </row>
@@ -4536,17 +4536,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>421.22</v>
+        <v>1389.43</v>
       </c>
       <c r="G90" t="n">
-        <v>332.55</v>
+        <v>1381.33</v>
       </c>
       <c r="H90" t="n">
-        <v>17.86</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[2070.57, 1967.13, 2546.67]</t>
+          <t>[3173.67, 3306.59, 3203.6]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[1816.86, 2029.92, 1865.53]</t>
+          <t>[1968.29, 1939.64, 1631.96]</t>
         </is>
       </c>
     </row>
@@ -4582,41 +4582,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>575.3200000000001</v>
+        <v>691.84</v>
       </c>
       <c r="G91" t="n">
-        <v>523.3200000000001</v>
+        <v>612.9</v>
       </c>
       <c r="H91" t="n">
-        <v>25.97</v>
+        <v>35.81</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[1842.07, 2520.75, 2893.92]</t>
+          <t>[2282.0, 2695.74, 2192.03]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[2029.92, 1865.53, 2167.03]</t>
+          <t>[1939.64, 1631.96, 1759.46]</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>91.41</v>
+        <v>79.7</v>
       </c>
       <c r="G92" t="n">
-        <v>65.41</v>
+        <v>69.89</v>
       </c>
       <c r="H92" t="n">
-        <v>7.71</v>
+        <v>7.03</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[1095.74, 992.94, 970.47]</t>
+          <t>[1094.88, 1081.14, 1088.97]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[1106.81, 962.8, 815.43]</t>
+          <t>[1035.3, 960.03, 1059.99]</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4693,22 +4693,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>116.99</v>
+        <v>101.41</v>
       </c>
       <c r="G93" t="n">
-        <v>105.02</v>
+        <v>81.97</v>
       </c>
       <c r="H93" t="n">
-        <v>11.15</v>
+        <v>7.35</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[998.47, 974.55, 1056.19]</t>
+          <t>[1044.36, 1052.29, 1072.37]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[962.8, 815.43, 1176.48]</t>
+          <t>[960.03, 1059.99, 1226.25]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4739,22 +4739,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>128.34</v>
+        <v>198.44</v>
       </c>
       <c r="G94" t="n">
-        <v>126.82</v>
+        <v>178.58</v>
       </c>
       <c r="H94" t="n">
-        <v>12.58</v>
+        <v>16.55</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[950.81, 1031.04, 1036.22]</t>
+          <t>[998.51, 1019.94, 1258.97]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[815.43, 1176.48, 1135.85]</t>
+          <t>[1059.99, 1226.25, 991.03]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>186.2</v>
+        <v>217.58</v>
       </c>
       <c r="G95" t="n">
-        <v>175.53</v>
+        <v>201.13</v>
       </c>
       <c r="H95" t="n">
-        <v>15.91</v>
+        <v>19.29</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[934.82, 943.32, 994.94]</t>
+          <t>[1058.88, 1306.39, 1093.28]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[1176.48, 1135.85, 902.53]</t>
+          <t>[1226.25, 991.03, 972.64]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>280.89</v>
+        <v>287.45</v>
       </c>
       <c r="G96" t="n">
-        <v>209.84</v>
+        <v>229.72</v>
       </c>
       <c r="H96" t="n">
-        <v>22.07</v>
+        <v>23.28</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[1202.11, 1376.1, 1222.5]</t>
+          <t>[1435.48, 1196.0, 1069.23]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[1135.85, 902.53, 1132.8]</t>
+          <t>[991.03, 972.64, 1047.88]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4877,22 +4877,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>302.77</v>
+        <v>238.65</v>
       </c>
       <c r="G97" t="n">
-        <v>258.35</v>
+        <v>191.86</v>
       </c>
       <c r="H97" t="n">
-        <v>26.85</v>
+        <v>17.06</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[1330.34, 1180.54, 1334.82]</t>
+          <t>[953.3, 858.63, 812.19]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[902.53, 1132.8, 1035.3]</t>
+          <t>[972.64, 1047.88, 1179.17]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4923,22 +4923,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>156.17</v>
+        <v>231.28</v>
       </c>
       <c r="G98" t="n">
-        <v>126.22</v>
+        <v>186.66</v>
       </c>
       <c r="H98" t="n">
-        <v>11.58</v>
+        <v>16.59</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[882.44, 937.6, 929.43]</t>
+          <t>[869.09, 821.47, 965.75]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[1132.8, 1035.3, 960.03]</t>
+          <t>[1047.88, 1179.17, 989.24]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4969,22 +4969,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>79.7</v>
+        <v>158.59</v>
       </c>
       <c r="G99" t="n">
-        <v>69.89</v>
+        <v>126.09</v>
       </c>
       <c r="H99" t="n">
-        <v>7.03</v>
+        <v>11.25</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[1094.88, 1081.14, 1088.97]</t>
+          <t>[921.79, 1080.55, 1072.35]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[1035.3, 960.03, 1059.99]</t>
+          <t>[1179.17, 989.24, 1101.94]</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5015,22 +5015,22 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>101.41</v>
+        <v>204.99</v>
       </c>
       <c r="G100" t="n">
-        <v>81.97</v>
+        <v>197.91</v>
       </c>
       <c r="H100" t="n">
-        <v>7.35</v>
+        <v>19.4</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[1044.36, 1052.29, 1072.37]</t>
+          <t>[1258.94, 1243.75, 1190.78]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[960.03, 1059.99, 1226.25]</t>
+          <t>[989.24, 1101.94, 1008.55]</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5061,22 +5061,22 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>198.44</v>
+        <v>63.85</v>
       </c>
       <c r="G101" t="n">
-        <v>178.58</v>
+        <v>53.16</v>
       </c>
       <c r="H101" t="n">
-        <v>16.55</v>
+        <v>5.55</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[998.51, 1019.94, 1258.97]</t>
+          <t>[1072.7, 1035.63, 1016.1]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[1059.99, 1226.25, 991.03]</t>
+          <t>[1101.94, 1008.55, 912.93]</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5107,22 +5107,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>157.04</v>
+        <v>282.02</v>
       </c>
       <c r="G102" t="n">
-        <v>147.87</v>
+        <v>276.77</v>
       </c>
       <c r="H102" t="n">
-        <v>14.72</v>
+        <v>26.23</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[802.66, 753.9, 946.78]</t>
+          <t>[707.29, 822.86, 791.47]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[882.31, 909.42, 1155.23]</t>
+          <t>[977.18, 1036.95, 1137.79]</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5153,22 +5153,22 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>146.83</v>
+        <v>182.88</v>
       </c>
       <c r="G103" t="n">
-        <v>144.78</v>
+        <v>172.48</v>
       </c>
       <c r="H103" t="n">
-        <v>14.25</v>
+        <v>16.35</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[773.4, 977.11, 852.22]</t>
+          <t>[905.29, 879.34, 806.79]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[909.42, 1155.23, 972.4]</t>
+          <t>[1036.95, 1137.79, 934.12]</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>143.22</v>
+        <v>189.12</v>
       </c>
       <c r="G104" t="n">
-        <v>134.74</v>
+        <v>179.55</v>
       </c>
       <c r="H104" t="n">
-        <v>12.72</v>
+        <v>16.42</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[1020.04, 897.36, 840.87]</t>
+          <t>[914.33, 838.51, 912.64]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[1155.23, 972.4, 1034.85]</t>
+          <t>[1137.79, 934.12, 1132.22]</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>97.79000000000001</v>
+        <v>168.55</v>
       </c>
       <c r="G105" t="n">
-        <v>82.25</v>
+        <v>144.62</v>
       </c>
       <c r="H105" t="n">
-        <v>8.27</v>
+        <v>13.97</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[928.34, 877.79, 940.29]</t>
+          <t>[896.76, 985.11, 751.45]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[972.4, 1034.85, 894.67]</t>
+          <t>[934.12, 1132.22, 1000.83]</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>91.11</v>
+        <v>184.83</v>
       </c>
       <c r="G106" t="n">
-        <v>68.69</v>
+        <v>179.64</v>
       </c>
       <c r="H106" t="n">
-        <v>6.94</v>
+        <v>18.1</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[888.7, 954.2, 859.8]</t>
+          <t>[996.9, 762.09, 727.23]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[1034.85, 894.67, 859.41]</t>
+          <t>[1132.22, 1000.83, 892.11]</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>154.05</v>
+        <v>141.17</v>
       </c>
       <c r="G107" t="n">
-        <v>129.67</v>
+        <v>119.39</v>
       </c>
       <c r="H107" t="n">
-        <v>13.8</v>
+        <v>12.56</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[998.84, 902.38, 735.33]</t>
+          <t>[794.21, 763.36, 900.53]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[894.67, 859.41, 977.18]</t>
+          <t>[1000.83, 892.11, 877.74]</t>
         </is>
       </c>
     </row>
@@ -5364,17 +5364,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5383,22 +5383,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>195.78</v>
+        <v>108.69</v>
       </c>
       <c r="G108" t="n">
-        <v>164.03</v>
+        <v>101.75</v>
       </c>
       <c r="H108" t="n">
-        <v>16.45</v>
+        <v>10.79</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[875.97, 710.7, 827.91]</t>
+          <t>[844.28, 1009.89, 921.54]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[859.41, 977.18, 1036.95]</t>
+          <t>[892.11, 877.74, 1046.8]</t>
         </is>
       </c>
     </row>
@@ -5410,17 +5410,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>282.02</v>
+        <v>116.88</v>
       </c>
       <c r="G109" t="n">
-        <v>276.77</v>
+        <v>113.56</v>
       </c>
       <c r="H109" t="n">
-        <v>26.23</v>
+        <v>12.14</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[707.29, 822.86, 791.47]</t>
+          <t>[1028.27, 940.6, 836.18]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[977.18, 1036.95, 1137.79]</t>
+          <t>[877.74, 1046.8, 920.13]</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5456,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5475,22 +5475,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>182.88</v>
+        <v>152.14</v>
       </c>
       <c r="G110" t="n">
-        <v>172.48</v>
+        <v>151.74</v>
       </c>
       <c r="H110" t="n">
-        <v>16.35</v>
+        <v>14.89</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[905.29, 879.34, 806.79]</t>
+          <t>[893.05, 782.74, 926.81]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[1036.95, 1137.79, 934.12]</t>
+          <t>[1046.8, 920.13, 1090.89]</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5502,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5521,22 +5521,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>189.12</v>
+        <v>88.78</v>
       </c>
       <c r="G111" t="n">
-        <v>179.55</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>16.42</v>
+        <v>8.35</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[914.33, 838.51, 912.64]</t>
+          <t>[820.04, 979.22, 900.6]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[1137.79, 934.12, 1132.22]</t>
+          <t>[920.13, 1090.89, 866.57]</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5563,26 +5563,26 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>252.34</v>
+        <v>445.25</v>
       </c>
       <c r="G112" t="n">
-        <v>203.53</v>
+        <v>402.02</v>
       </c>
       <c r="H112" t="n">
-        <v>15.85</v>
+        <v>29.59</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[960.3, 998.74, 1155.67]</t>
+          <t>[799.48, 918.33, 1038.45]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[1358.71, 1174.79, 1119.53]</t>
+          <t>[1466.16, 1237.16, 1259.01]</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5609,26 +5609,26 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>88.08</v>
+        <v>70.05</v>
       </c>
       <c r="G113" t="n">
-        <v>67.36</v>
+        <v>57.46</v>
       </c>
       <c r="H113" t="n">
-        <v>5.95</v>
+        <v>4.59</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[1127.09, 1264.11, 1103.06]</t>
+          <t>[1149.36, 1258.16, 1353.42]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[1174.79, 1119.53, 1112.85]</t>
+          <t>[1237.16, 1259.01, 1269.69]</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5655,26 +5655,26 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>135.87</v>
+        <v>363.82</v>
       </c>
       <c r="G114" t="n">
-        <v>111.33</v>
+        <v>255.01</v>
       </c>
       <c r="H114" t="n">
-        <v>10.34</v>
+        <v>17.24</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[1277.61, 1114.41, 1213.9]</t>
+          <t>[1291.64, 1383.08, 2158.95]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[1119.53, 1112.85, 1039.56]</t>
+          <t>[1259.01, 1269.69, 1539.94]</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5686,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5701,26 +5701,26 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>394.83</v>
+        <v>355.28</v>
       </c>
       <c r="G115" t="n">
-        <v>279.25</v>
+        <v>247.89</v>
       </c>
       <c r="H115" t="n">
-        <v>41.58</v>
+        <v>16.6</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[1077.75, 1172.27, 1285.53]</t>
+          <t>[1372.0, 2145.7, 1445.98]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[1112.85, 1039.56, 615.58]</t>
+          <t>[1269.69, 1539.94, 1481.59]</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5747,26 +5747,26 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>480.82</v>
+        <v>325.55</v>
       </c>
       <c r="G116" t="n">
-        <v>427.13</v>
+        <v>209.18</v>
       </c>
       <c r="H116" t="n">
-        <v>69.5</v>
+        <v>13.65</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[1179.69, 1292.72, 1009.98]</t>
+          <t>[2100.28, 1418.78, 1382.23]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[1039.56, 615.58, 545.87]</t>
+          <t>[1539.94, 1481.59, 1377.83]</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5793,26 +5793,26 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>481.72</v>
+        <v>118.02</v>
       </c>
       <c r="G117" t="n">
-        <v>464.07</v>
+        <v>113.14</v>
       </c>
       <c r="H117" t="n">
-        <v>68.41</v>
+        <v>7.84</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[1248.32, 986.4, 1147.21]</t>
+          <t>[1322.32, 1297.64, 1336.03]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[615.58, 545.87, 1466.16]</t>
+          <t>[1481.59, 1377.83, 1435.98]</t>
         </is>
       </c>
     </row>
@@ -5824,12 +5824,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5843,22 +5843,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>363.86</v>
+        <v>122.09</v>
       </c>
       <c r="G118" t="n">
-        <v>328.33</v>
+        <v>98.56</v>
       </c>
       <c r="H118" t="n">
-        <v>32.59</v>
+        <v>8.25</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[790.66, 918.13, 1044.99]</t>
+          <t>[1342.97, 1374.43, 1311.25]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[545.87, 1466.16, 1237.16]</t>
+          <t>[1377.83, 1435.98, 1111.97]</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5889,22 +5889,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>445.25</v>
+        <v>190.36</v>
       </c>
       <c r="G119" t="n">
-        <v>402.02</v>
+        <v>169.92</v>
       </c>
       <c r="H119" t="n">
-        <v>29.59</v>
+        <v>15.28</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[799.48, 918.33, 1038.45]</t>
+          <t>[1384.74, 1319.3, 1314.1]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[1466.16, 1237.16, 1259.01]</t>
+          <t>[1435.98, 1111.97, 1062.91]</t>
         </is>
       </c>
     </row>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>70.05</v>
+        <v>218.5</v>
       </c>
       <c r="G120" t="n">
-        <v>57.46</v>
+        <v>214.37</v>
       </c>
       <c r="H120" t="n">
-        <v>4.59</v>
+        <v>20.24</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[1149.36, 1258.16, 1353.42]</t>
+          <t>[1333.08, 1325.36, 1148.32]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[1237.16, 1259.01, 1269.69]</t>
+          <t>[1111.97, 1062.91, 988.78]</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>363.82</v>
+        <v>168.77</v>
       </c>
       <c r="G121" t="n">
-        <v>255.01</v>
+        <v>165.05</v>
       </c>
       <c r="H121" t="n">
-        <v>17.24</v>
+        <v>15.69</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[1291.64, 1383.08, 2158.95]</t>
+          <t>[1259.25, 1104.61, 900.21]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[1259.01, 1269.69, 1539.94]</t>
+          <t>[1062.91, 988.78, 1083.18]</t>
         </is>
       </c>
     </row>
@@ -6008,12 +6008,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1.99</v>
+        <v>16</v>
       </c>
       <c r="G122" t="n">
-        <v>1.34</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>42.51</v>
+        <v>70.89</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[1.57, 1.53, 1.47]</t>
+          <t>[1.79, 3.74, 3.69]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[1.5, 1.0, 4.88]</t>
+          <t>[1.2, 31.41, 2.1]</t>
         </is>
       </c>
     </row>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2.84</v>
+        <v>16.02</v>
       </c>
       <c r="G123" t="n">
-        <v>2.48</v>
+        <v>10.16</v>
       </c>
       <c r="H123" t="n">
-        <v>66.70999999999999</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[1.53, 1.47, 1.03]</t>
+          <t>[3.73, 3.68, 2.83]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[1.0, 4.88, 4.53]</t>
+          <t>[31.41, 2.1, 1.6]</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5.89</v>
+        <v>1.21</v>
       </c>
       <c r="G124" t="n">
-        <v>5.29</v>
+        <v>1.01</v>
       </c>
       <c r="H124" t="n">
-        <v>78.16</v>
+        <v>53.12</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[1.47, 1.03, 1.3]</t>
+          <t>[3.75, 2.89, 41.17]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[4.88, 4.53, 10.26]</t>
+          <t>[2.1, 1.6, 41.06]</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>5.57</v>
+        <v>0.8</v>
       </c>
       <c r="G125" t="n">
-        <v>4.41</v>
+        <v>0.65</v>
       </c>
       <c r="H125" t="n">
-        <v>86.95</v>
+        <v>39.69</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[1.03, 1.3, 1.57]</t>
+          <t>[2.87, 40.94, 1.95]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[4.53, 10.26, 0.8]</t>
+          <t>[1.6, 41.06, 1.4]</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6211,22 +6211,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>9.550000000000001</v>
+        <v>5.59</v>
       </c>
       <c r="G126" t="n">
-        <v>7.96</v>
+        <v>3.51</v>
       </c>
       <c r="H126" t="n">
-        <v>103.1</v>
+        <v>42.51</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[1.63, 1.97, 3.75]</t>
+          <t>[40.72, 1.94, 1.29]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[10.26, 0.8, 17.82]</t>
+          <t>[41.06, 1.4, 10.95]</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6257,22 +6257,22 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>8.119999999999999</v>
+        <v>5.61</v>
       </c>
       <c r="G127" t="n">
-        <v>5.26</v>
+        <v>3.73</v>
       </c>
       <c r="H127" t="n">
-        <v>92.44</v>
+        <v>48.58</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[2.01, 3.82, 1.78]</t>
+          <t>[1.94, 1.29, 6.31]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[0.8, 17.82, 1.2]</t>
+          <t>[1.4, 10.95, 5.3]</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6303,22 +6303,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>17.94</v>
+        <v>5.61</v>
       </c>
       <c r="G128" t="n">
-        <v>14.11</v>
+        <v>3.63</v>
       </c>
       <c r="H128" t="n">
-        <v>71.23</v>
+        <v>37.05</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[3.79, 1.76, 3.68]</t>
+          <t>[1.29, 6.29, 5.84]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[17.82, 1.2, 31.41]</t>
+          <t>[10.95, 5.3, 5.6]</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6349,22 +6349,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>16</v>
+        <v>5.8</v>
       </c>
       <c r="G129" t="n">
-        <v>9.949999999999999</v>
+        <v>3.82</v>
       </c>
       <c r="H129" t="n">
-        <v>70.89</v>
+        <v>104.19</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[1.79, 3.74, 3.69]</t>
+          <t>[6.41, 5.95, 13.48]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[1.2, 31.41, 2.1]</t>
+          <t>[5.3, 5.6, 3.5]</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6395,22 +6395,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>16.02</v>
+        <v>6.98</v>
       </c>
       <c r="G130" t="n">
-        <v>10.16</v>
+        <v>5.72</v>
       </c>
       <c r="H130" t="n">
-        <v>80.01000000000001</v>
+        <v>125.81</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[3.73, 3.68, 2.83]</t>
+          <t>[5.94, 13.46, 1.05]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[31.41, 2.1, 1.6]</t>
+          <t>[5.6, 3.5, 7.9]</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1.21</v>
+        <v>15.03</v>
       </c>
       <c r="G131" t="n">
-        <v>1.01</v>
+        <v>13.29</v>
       </c>
       <c r="H131" t="n">
-        <v>53.12</v>
+        <v>2686.61</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[3.75, 2.89, 41.17]</t>
+          <t>[13.45, 1.05, 23.37]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[2.1, 1.6, 41.06]</t>
+          <t>[3.5, 7.9, 0.3]</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6487,22 +6487,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>4144.56</v>
+        <v>1388.59</v>
       </c>
       <c r="G132" t="n">
-        <v>4058.57</v>
+        <v>1376.84</v>
       </c>
       <c r="H132" t="n">
-        <v>567.77</v>
+        <v>245.49</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[3741.98, 4671.61, 5922.64]</t>
+          <t>[2167.85, 1632.55, 2233.21]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>[719.0, 599.01, 842.52]</t>
+          <t>[921.96, 379.6, 601.52]</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6533,22 +6533,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3347.63</v>
+        <v>2425.53</v>
       </c>
       <c r="G133" t="n">
-        <v>3344.68</v>
+        <v>2061.92</v>
       </c>
       <c r="H133" t="n">
-        <v>448.45</v>
+        <v>323.75</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[3933.94, 4020.08, 4377.38]</t>
+          <t>[1484.25, 1815.35, 4675.55]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>[599.01, 842.52, 855.84]</t>
+          <t>[379.6, 601.52, 808.27]</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6579,22 +6579,22 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2568.98</v>
+        <v>2535.11</v>
       </c>
       <c r="G134" t="n">
-        <v>2521.69</v>
+        <v>2316.57</v>
       </c>
       <c r="H134" t="n">
-        <v>321.35</v>
+        <v>310.35</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[3301.02, 2810.75, 3861.76]</t>
+          <t>[1557.75, 3354.98, 4200.98]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>[842.52, 855.84, 710.09]</t>
+          <t>[601.52, 808.27, 754.21]</t>
         </is>
       </c>
     </row>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6625,22 +6625,22 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2744.71</v>
+        <v>2596.86</v>
       </c>
       <c r="G135" t="n">
-        <v>2543.41</v>
+        <v>2578.83</v>
       </c>
       <c r="H135" t="n">
-        <v>365.52</v>
+        <v>398.38</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[2429.42, 2794.32, 4613.99]</t>
+          <t>[3014.71, 3329.49, 3463.59]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>[855.84, 710.09, 641.57]</t>
+          <t>[808.27, 754.21, 508.83]</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6671,22 +6671,22 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2963.08</v>
+        <v>2108.18</v>
       </c>
       <c r="G136" t="n">
-        <v>2846.27</v>
+        <v>2106.55</v>
       </c>
       <c r="H136" t="n">
-        <v>427.06</v>
+        <v>396.39</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[2496.43, 3599.16, 4462.26]</t>
+          <t>[2867.52, 2510.69, 2632.09]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>[710.09, 641.57, 667.37]</t>
+          <t>[754.21, 508.83, 427.6]</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6717,22 +6717,22 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2648.55</v>
+        <v>1741.62</v>
       </c>
       <c r="G137" t="n">
-        <v>2645.71</v>
+        <v>1724.31</v>
       </c>
       <c r="H137" t="n">
-        <v>362.85</v>
+        <v>333.24</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[3141.52, 3304.93, 3721.6]</t>
+          <t>[2156.67, 1897.5, 2673.98]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>[641.57, 667.37, 921.96]</t>
+          <t>[508.83, 427.6, 618.8]</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6763,22 +6763,22 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1895.13</v>
+        <v>1323.36</v>
       </c>
       <c r="G138" t="n">
-        <v>1884.25</v>
+        <v>1315.7</v>
       </c>
       <c r="H138" t="n">
-        <v>332.91</v>
+        <v>208.07</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[2777.07, 2540.1, 2304.51]</t>
+          <t>[1607.94, 1873.36, 2552.08]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>[667.37, 921.96, 379.6]</t>
+          <t>[427.6, 618.8, 1039.88]</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6809,22 +6809,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1388.59</v>
+        <v>1133.79</v>
       </c>
       <c r="G139" t="n">
-        <v>1376.84</v>
+        <v>1094.47</v>
       </c>
       <c r="H139" t="n">
-        <v>245.49</v>
+        <v>147.14</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[2167.85, 1632.55, 2233.21]</t>
+          <t>[1606.08, 1837.55, 2228.81]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[921.96, 379.6, 601.52]</t>
+          <t>[618.8, 1039.88, 730.33]</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6855,22 +6855,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2425.53</v>
+        <v>1059.96</v>
       </c>
       <c r="G140" t="n">
-        <v>2061.92</v>
+        <v>1009.25</v>
       </c>
       <c r="H140" t="n">
-        <v>323.75</v>
+        <v>119.35</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[1484.25, 1815.35, 4675.55]</t>
+          <t>[1643.45, 1758.12, 2273.11]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[379.6, 601.52, 808.27]</t>
+          <t>[1039.88, 730.33, 876.72]</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6901,22 +6901,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2535.11</v>
+        <v>1375.51</v>
       </c>
       <c r="G141" t="n">
-        <v>2316.57</v>
+        <v>1317.25</v>
       </c>
       <c r="H141" t="n">
-        <v>310.35</v>
+        <v>154.69</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[1557.75, 3354.98, 4200.98]</t>
+          <t>[1666.53, 2028.98, 2774.71]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>[601.52, 808.27, 754.21]</t>
+          <t>[730.33, 876.72, 911.41]</t>
         </is>
       </c>
     </row>
@@ -6928,12 +6928,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6943,26 +6943,26 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>163.13</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G142" t="n">
-        <v>160.43</v>
+        <v>58.71</v>
       </c>
       <c r="H142" t="n">
-        <v>8.51</v>
+        <v>3.04</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[1941.28, 1941.28, 1941.28]</t>
+          <t>[1850.37, 1881.95, 1878.85]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[1751.4, 1821.3, 2112.7]</t>
+          <t>[1936.9, 1862.4, 1948.9]</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6989,26 +6989,26 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>132.2</v>
+        <v>127.44</v>
       </c>
       <c r="G143" t="n">
-        <v>125.86</v>
+        <v>99.34</v>
       </c>
       <c r="H143" t="n">
-        <v>6.3</v>
+        <v>4.86</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[1931.32, 1931.32, 1931.32]</t>
+          <t>[1881.95, 1878.85, 1890.29]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[1821.3, 2112.7, 2017.5]</t>
+          <t>[1862.4, 1948.9, 2098.7]</t>
         </is>
       </c>
     </row>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7035,26 +7035,26 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>152.69</v>
+        <v>154.23</v>
       </c>
       <c r="G144" t="n">
-        <v>147.22</v>
+        <v>143.08</v>
       </c>
       <c r="H144" t="n">
-        <v>7.55</v>
+        <v>6.89</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[1925.93, 1925.93, 1925.93]</t>
+          <t>[1824.73, 1877.59, 2142.04]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[2112.7, 2017.5, 1762.6]</t>
+          <t>[1948.9, 2098.7, 2226.0]</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7081,26 +7081,26 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>164.47</v>
+        <v>143.87</v>
       </c>
       <c r="G145" t="n">
-        <v>155.52</v>
+        <v>131.84</v>
       </c>
       <c r="H145" t="n">
-        <v>8.720000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[1934.05, 1934.05, 1934.05]</t>
+          <t>[1896.15, 2164.53, 1747.69]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[2017.5, 1762.6, 1722.4]</t>
+          <t>[2098.7, 2226.0, 1879.2]</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7127,26 +7127,26 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>213.21</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="G146" t="n">
-        <v>211.34</v>
+        <v>65.92</v>
       </c>
       <c r="H146" t="n">
-        <v>12.27</v>
+        <v>3.53</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[1937.61, 1937.61, 1937.61]</t>
+          <t>[2193.33, 1769.45, 1738.84]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[1762.6, 1722.4, 1693.8]</t>
+          <t>[2226.0, 1879.2, 1683.5]</t>
         </is>
       </c>
     </row>
@@ -7158,12 +7158,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7173,26 +7173,26 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>158.16</v>
+        <v>69.2</v>
       </c>
       <c r="G147" t="n">
-        <v>147.77</v>
+        <v>58.43</v>
       </c>
       <c r="H147" t="n">
-        <v>8.44</v>
+        <v>3.23</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[1945.0, 1827.97, 1850.37]</t>
+          <t>[1773.89, 1738.85, 1807.06]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[1722.4, 1693.8, 1936.9]</t>
+          <t>[1879.2, 1683.5, 1821.7]</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7219,26 +7219,26 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>92.86</v>
+        <v>248.83</v>
       </c>
       <c r="G148" t="n">
-        <v>80.08</v>
+        <v>166.34</v>
       </c>
       <c r="H148" t="n">
-        <v>4.48</v>
+        <v>7.77</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[1827.97, 1850.37, 1881.95]</t>
+          <t>[1748.15, 1813.35, 1813.78]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[1693.8, 1936.9, 1862.4]</t>
+          <t>[1683.5, 1821.7, 2239.8]</t>
         </is>
       </c>
     </row>
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7265,26 +7265,26 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>65.26000000000001</v>
+        <v>326.25</v>
       </c>
       <c r="G149" t="n">
-        <v>58.71</v>
+        <v>272.49</v>
       </c>
       <c r="H149" t="n">
-        <v>3.04</v>
+        <v>12.28</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[1850.37, 1881.95, 1878.85]</t>
+          <t>[1798.43, 1801.48, 1868.81]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[1936.9, 1862.4, 1948.9]</t>
+          <t>[1821.7, 2239.8, 2224.7]</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7311,26 +7311,26 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>127.44</v>
+        <v>330.32</v>
       </c>
       <c r="G150" t="n">
-        <v>99.34</v>
+        <v>299.34</v>
       </c>
       <c r="H150" t="n">
-        <v>4.86</v>
+        <v>13.88</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[1881.95, 1878.85, 1890.29]</t>
+          <t>[1802.58, 1871.79, 1828.58]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[1862.4, 1948.9, 2098.7]</t>
+          <t>[2239.8, 2224.7, 1720.7]</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7357,26 +7357,26 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>154.23</v>
+        <v>332.26</v>
       </c>
       <c r="G151" t="n">
-        <v>143.08</v>
+        <v>268.93</v>
       </c>
       <c r="H151" t="n">
-        <v>6.89</v>
+        <v>12.57</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[1824.73, 1877.59, 2142.04]</t>
+          <t>[1762.6, 1722.4, 1693.8]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[1948.9, 2098.7, 2226.0]</t>
+          <t>[2224.7, 1720.7, 2036.8]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>117.55</v>
+        <v>90.78</v>
       </c>
       <c r="G152" t="n">
-        <v>97.63</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="H152" t="n">
-        <v>188.89</v>
+        <v>205.54</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[264.55, 71.02, 29.04]</t>
+          <t>[84.84, 9.59, 0.43]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[83.1, 160.8, 7.4]</t>
+          <t>[13.8, 9.8, 140.7]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>119.79</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="G153" t="n">
-        <v>100.16</v>
+        <v>65.89</v>
       </c>
       <c r="H153" t="n">
-        <v>91.19</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[17.79, 14.73, 25.26]</t>
+          <t>[9.59, 0.43, 0.9]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[160.8, 7.4, 175.4]</t>
+          <t>[9.8, 140.7, 58.1]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>157.89</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>153.47</v>
+        <v>73.25</v>
       </c>
       <c r="H154" t="n">
-        <v>569.65</v>
+        <v>79.03</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[121.43, 32.22, 32.22]</t>
+          <t>[0.43, 0.9, 79.48]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[7.4, 175.4, 235.4]</t>
+          <t>[140.7, 58.1, 57.2]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(4, 0, 1)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>202.77</v>
+        <v>3972.46</v>
       </c>
       <c r="G155" t="n">
-        <v>201.59</v>
+        <v>3026.2</v>
       </c>
       <c r="H155" t="n">
-        <v>91.78</v>
+        <v>5244.02</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[3.72, 12.15, 44.16]</t>
+          <t>[2762.37, 6383.8, 232.07]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[175.4, 235.4, 254.0]</t>
+          <t>[58.1, 57.2, 279.8]</t>
         </is>
       </c>
     </row>
@@ -7572,41 +7572,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>170.85</v>
+        <v>130.96</v>
       </c>
       <c r="G156" t="n">
-        <v>163.93</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>81.29000000000001</v>
+        <v>106.37</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[43.68, 50.17, 20.86]</t>
+          <t>[112.21, 59.82, 9.53]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[235.4, 254.0, 117.1]</t>
+          <t>[57.2, 279.8, 3.9]</t>
         </is>
       </c>
     </row>
@@ -7618,41 +7618,41 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>59.01</v>
+        <v>136.16</v>
       </c>
       <c r="G157" t="n">
-        <v>58.29</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="H157" t="n">
-        <v>192.88</v>
+        <v>78.69</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[307.94, 67.2, 84.84]</t>
+          <t>[44.02, 8.8, 7.45]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[254.0, 117.1, 13.8]</t>
+          <t>[279.8, 3.9, 5.9]</t>
         </is>
       </c>
     </row>
@@ -7664,41 +7664,41 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>50.12</v>
+        <v>26.92</v>
       </c>
       <c r="G158" t="n">
-        <v>40.38</v>
+        <v>21.15</v>
       </c>
       <c r="H158" t="n">
-        <v>186.51</v>
+        <v>188.16</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[67.2, 84.84, 9.59]</t>
+          <t>[23.57, 7.45, 82.15]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[117.1, 13.8, 9.8]</t>
+          <t>[3.9, 5.9, 124.4]</t>
         </is>
       </c>
     </row>
@@ -7710,41 +7710,41 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>90.78</v>
+        <v>62.84</v>
       </c>
       <c r="G159" t="n">
-        <v>70.51000000000001</v>
+        <v>48.69</v>
       </c>
       <c r="H159" t="n">
-        <v>205.54</v>
+        <v>35.44</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[84.84, 9.59, 0.43]</t>
+          <t>[3.84, 79.52, 181.07]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[13.8, 9.8, 140.7]</t>
+          <t>[5.9, 124.4, 280.2]</t>
         </is>
       </c>
     </row>
@@ -7756,41 +7756,41 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>87.45999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="G160" t="n">
-        <v>65.89</v>
+        <v>85.45</v>
       </c>
       <c r="H160" t="n">
-        <v>66.76000000000001</v>
+        <v>44.23</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[9.59, 0.43, 0.9]</t>
+          <t>[90.03, 180.15, 297.73]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[9.8, 140.7, 58.1]</t>
+          <t>[124.4, 280.2, 175.8]</t>
         </is>
       </c>
     </row>
@@ -7802,41 +7802,41 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>88.40000000000001</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="G161" t="n">
-        <v>73.25</v>
+        <v>81.48</v>
       </c>
       <c r="H161" t="n">
-        <v>79.03</v>
+        <v>90.47</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[0.43, 0.9, 79.48]</t>
+          <t>[205.11, 298.26, 73.69]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[140.7, 58.1, 57.2]</t>
+          <t>[280.2, 175.8, 26.8]</t>
         </is>
       </c>
     </row>
@@ -7848,41 +7848,41 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>5.53</v>
+        <v>0.92</v>
       </c>
       <c r="G162" t="n">
-        <v>5.23</v>
+        <v>0.74</v>
       </c>
       <c r="H162" t="n">
-        <v>1.235430909463902e+24</v>
+        <v>11.53</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[4.75, 3.34, 7.61]</t>
+          <t>[3.45, 10.21, 6.36]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[3.1, 8.7, 6.0]</t>
         </is>
       </c>
     </row>
@@ -7894,41 +7894,41 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>2.361180880251581e+23</v>
+        <v>31.18</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0]</t>
+          <t>[9.39, 5.96, 3.7]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[8.7, 6.0, 2.0]</t>
         </is>
       </c>
     </row>
@@ -7940,41 +7940,41 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.82</v>
+        <v>1.6</v>
       </c>
       <c r="G164" t="n">
-        <v>0.71</v>
+        <v>1.4</v>
       </c>
       <c r="H164" t="n">
-        <v>1.671382184816476e+23</v>
+        <v>33.66</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[0.12, 1.0, 1.0]</t>
+          <t>[5.61, 3.53, 10.32]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[6.0, 2.0, 12.6]</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8001,26 +8001,26 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="H165" t="n">
-        <v>6.161368039505202e+19</v>
+        <v>519840007107950.2</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[3.72, 10.76, 0.0]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[2.0, 12.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8032,41 +8032,41 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>5.54</v>
+        <v>3.47</v>
       </c>
       <c r="G166" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
-        <v>33.33</v>
+        <v>4.539366168374644e+16</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[6.59, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 9.6]</t>
+          <t>[12.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8078,32 +8078,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>1.08803288343453e+18</v>
+        <v>2.64904601873846e+16</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[0.0, 9.6, 3.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>100</v>
+        <v>2.349916775524992e+17</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[9.6, 3.1, 8.7]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>11.53</v>
+        <v>133.33</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[3.45, 10.21, 6.36]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[3.1, 8.7, 6.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8216,12 +8216,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>31.18</v>
+        <v>533.33</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[9.39, 5.96, 3.7]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[8.7, 6.0, 2.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8281,22 +8281,22 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1.6</v>
+        <v>0.06</v>
       </c>
       <c r="G171" t="n">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="H171" t="n">
-        <v>33.66</v>
+        <v>433.68</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[5.61, 3.53, 10.32]</t>
+          <t>[0.0, 0.0, 9.6]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[6.0, 2.0, 12.6]</t>
+          <t>[0.0, 0.0, 9.5]</t>
         </is>
       </c>
     </row>
@@ -8308,41 +8308,41 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>141.97</v>
+        <v>156.46</v>
       </c>
       <c r="G172" t="n">
-        <v>116.36</v>
+        <v>149.52</v>
       </c>
       <c r="H172" t="n">
-        <v>36.08</v>
+        <v>96.03</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[191.68, 131.37, 222.44]</t>
+          <t>[308.6, 327.55, 286.47]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[252.7, 362.73, 279.14]</t>
+          <t>[146.9, 128.7, 374.48]</t>
         </is>
       </c>
     </row>
@@ -8354,41 +8354,41 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>125.88</v>
+        <v>128.42</v>
       </c>
       <c r="G173" t="n">
-        <v>88.05</v>
+        <v>124.03</v>
       </c>
       <c r="H173" t="n">
-        <v>25.42</v>
+        <v>54.3</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[147.72, 247.58, 291.98]</t>
+          <t>[254.54, 210.59, 303.39]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[362.73, 279.14, 309.56]</t>
+          <t>[128.7, 374.48, 385.73]</t>
         </is>
       </c>
     </row>
@@ -8400,41 +8400,41 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>105.04</v>
+        <v>180.45</v>
       </c>
       <c r="G174" t="n">
-        <v>101.5</v>
+        <v>179.24</v>
       </c>
       <c r="H174" t="n">
-        <v>36.41</v>
+        <v>44.88</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[355.5, 398.72, 400.89]</t>
+          <t>[167.35, 228.85, 275.63]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[279.14, 309.56, 261.9]</t>
+          <t>[374.48, 385.73, 449.35]</t>
         </is>
       </c>
     </row>
@@ -8446,41 +8446,41 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>119.3</v>
+        <v>95.08</v>
       </c>
       <c r="G175" t="n">
-        <v>115.1</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="H175" t="n">
-        <v>58.45</v>
+        <v>25.31</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[396.71, 361.15, 304.31]</t>
+          <t>[301.52, 379.72, 195.95]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[309.56, 261.9, 145.4]</t>
+          <t>[385.73, 449.35, 319.17]</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8507,26 +8507,26 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>100.13</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="G176" t="n">
-        <v>99.45</v>
+        <v>67.69</v>
       </c>
       <c r="H176" t="n">
-        <v>45.71</v>
+        <v>21.88</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[351.92, 261.28, 308.64]</t>
+          <t>[413.44, 216.29, 188.57]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[261.9, 145.4, 401.1]</t>
+          <t>[449.35, 319.17, 252.85]</t>
         </is>
       </c>
     </row>
@@ -8538,41 +8538,41 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>124.37</v>
+        <v>66.23</v>
       </c>
       <c r="G177" t="n">
-        <v>122.8</v>
+        <v>58.62</v>
       </c>
       <c r="H177" t="n">
-        <v>66.72</v>
+        <v>20.75</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[246.23, 282.14, 295.5]</t>
+          <t>[222.5, 194.81, 255.69]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[145.4, 401.1, 146.9]</t>
+          <t>[319.17, 252.85, 234.53]</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8599,26 +8599,26 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>121.71</v>
+        <v>56.53</v>
       </c>
       <c r="G178" t="n">
-        <v>117.17</v>
+        <v>54.24</v>
       </c>
       <c r="H178" t="n">
-        <v>59.54</v>
+        <v>17.06</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[237.99, 234.43, 229.56]</t>
+          <t>[220.55, 295.54, 490.52]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[401.1, 146.9, 128.7]</t>
+          <t>[252.85, 234.53, 559.95]</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8649,22 +8649,22 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>156.46</v>
+        <v>138.2</v>
       </c>
       <c r="G179" t="n">
-        <v>149.52</v>
+        <v>113.49</v>
       </c>
       <c r="H179" t="n">
-        <v>96.03</v>
+        <v>26.38</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[308.6, 327.55, 286.47]</t>
+          <t>[309.8, 518.09, 341.09]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[146.9, 128.7, 374.48]</t>
+          <t>[234.53, 559.95, 564.43]</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8695,22 +8695,22 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>128.42</v>
+        <v>324.71</v>
       </c>
       <c r="G180" t="n">
-        <v>124.03</v>
+        <v>279.8</v>
       </c>
       <c r="H180" t="n">
-        <v>54.3</v>
+        <v>40.58</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[254.54, 210.59, 303.39]</t>
+          <t>[470.95, 305.04, 328.94]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[128.7, 374.48, 385.73]</t>
+          <t>[559.95, 564.43, 819.96]</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8741,22 +8741,22 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>180.45</v>
+        <v>493.33</v>
       </c>
       <c r="G181" t="n">
-        <v>179.24</v>
+        <v>460.63</v>
       </c>
       <c r="H181" t="n">
-        <v>44.88</v>
+        <v>57.79</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[167.35, 228.85, 275.63]</t>
+          <t>[323.44, 352.47, 240.87]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[374.48, 385.73, 449.35]</t>
+          <t>[564.43, 819.96, 914.28]</t>
         </is>
       </c>
     </row>
@@ -8768,41 +8768,41 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>88.78</v>
+        <v>227.46</v>
       </c>
       <c r="G182" t="n">
-        <v>73.14</v>
+        <v>213.15</v>
       </c>
       <c r="H182" t="n">
-        <v>25.86</v>
+        <v>42.25</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[234.43, 168.86, 232.78]</t>
+          <t>[254.41, 158.16, 559.65]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[277.85, 312.87, 200.81]</t>
+          <t>[397.76, 482.39, 731.53]</t>
         </is>
       </c>
     </row>
@@ -8814,17 +8814,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>95.28</v>
+        <v>232.6</v>
       </c>
       <c r="G183" t="n">
-        <v>93.06999999999999</v>
+        <v>218.36</v>
       </c>
       <c r="H183" t="n">
-        <v>42.6</v>
+        <v>41.79</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[196.79, 297.43, 222.66]</t>
+          <t>[180.42, 621.2, 266.39]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[312.87, 200.81, 156.16]</t>
+          <t>[482.39, 731.53, 509.18]</t>
         </is>
       </c>
     </row>
@@ -8860,41 +8860,41 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>132.77</v>
+        <v>115.6</v>
       </c>
       <c r="G184" t="n">
-        <v>126.92</v>
+        <v>107.44</v>
       </c>
       <c r="H184" t="n">
-        <v>246.5</v>
+        <v>21.48</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[308.72, 247.79, 210.13]</t>
+          <t>[811.3, 341.48, 438.12]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[200.81, 156.16, 28.9]</t>
+          <t>[731.53, 509.18, 363.28]</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8925,22 +8925,22 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>113.79</v>
+        <v>145.12</v>
       </c>
       <c r="G185" t="n">
-        <v>110.22</v>
+        <v>135.61</v>
       </c>
       <c r="H185" t="n">
-        <v>205.54</v>
+        <v>30.78</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[228.75, 169.69, 258.59]</t>
+          <t>[331.32, 426.12, 247.92]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[156.16, 28.9, 141.33]</t>
+          <t>[509.18, 363.28, 414.05]</t>
         </is>
       </c>
     </row>
@@ -8952,41 +8952,41 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>103.32</v>
+        <v>164.93</v>
       </c>
       <c r="G186" t="n">
-        <v>81.53</v>
+        <v>158.73</v>
       </c>
       <c r="H186" t="n">
-        <v>202.97</v>
+        <v>36.69</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[187.51, 224.15, 217.36]</t>
+          <t>[480.51, 276.07, 275.84]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[28.9, 141.33, 214.21]</t>
+          <t>[363.28, 414.05, 496.82]</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9017,22 +9017,22 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>81.63</v>
+        <v>317.64</v>
       </c>
       <c r="G187" t="n">
-        <v>66.06999999999999</v>
+        <v>289.02</v>
       </c>
       <c r="H187" t="n">
-        <v>25.14</v>
+        <v>50.98</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[188.33, 194.96, 265.81]</t>
+          <t>[255.27, 258.07, 236.11]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[141.33, 214.21, 397.76]</t>
+          <t>[414.05, 496.82, 705.66]</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9063,22 +9063,22 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>214</v>
+        <v>350.48</v>
       </c>
       <c r="G188" t="n">
-        <v>176.5</v>
+        <v>335.99</v>
       </c>
       <c r="H188" t="n">
-        <v>42.2</v>
+        <v>55.56</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[176.31, 238.92, 149.64]</t>
+          <t>[295.35, 265.59, 208.09]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[214.21, 397.76, 482.39]</t>
+          <t>[496.82, 705.66, 574.51]</t>
         </is>
       </c>
     </row>
@@ -9090,12 +9090,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9109,22 +9109,22 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>227.46</v>
+        <v>465.8</v>
       </c>
       <c r="G189" t="n">
-        <v>213.15</v>
+        <v>450.46</v>
       </c>
       <c r="H189" t="n">
-        <v>42.25</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[254.41, 158.16, 559.65]</t>
+          <t>[306.61, 236.55, 67.63]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[397.76, 482.39, 731.53]</t>
+          <t>[705.66, 574.51, 682.01]</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9155,22 +9155,22 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>232.6</v>
+        <v>444.2</v>
       </c>
       <c r="G190" t="n">
-        <v>218.36</v>
+        <v>423.64</v>
       </c>
       <c r="H190" t="n">
-        <v>41.79</v>
+        <v>63.2</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[180.42, 621.2, 266.39]</t>
+          <t>[310.16, 90.78, 314.79]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[482.39, 731.53, 509.18]</t>
+          <t>[574.51, 682.01, 730.13]</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9201,22 +9201,22 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>115.6</v>
+        <v>494.43</v>
       </c>
       <c r="G191" t="n">
-        <v>107.44</v>
+        <v>484.16</v>
       </c>
       <c r="H191" t="n">
-        <v>21.48</v>
+        <v>61.84</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[811.3, 341.48, 438.12]</t>
+          <t>[115.82, 387.17, 435.22]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[731.53, 509.18, 363.28]</t>
+          <t>[682.01, 730.13, 978.55]</t>
         </is>
       </c>
     </row>
@@ -9228,41 +9228,41 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>504.23</v>
+        <v>184.52</v>
       </c>
       <c r="G192" t="n">
-        <v>449.03</v>
+        <v>182.62</v>
       </c>
       <c r="H192" t="n">
-        <v>59.03</v>
+        <v>26.06</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[244.68, 429.69, 345.42]</t>
+          <t>[554.65, 516.08, 484.87]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[891.03, 302.31, 918.78]</t>
+          <t>[700.6, 711.12, 691.74]</t>
         </is>
       </c>
     </row>
@@ -9274,41 +9274,41 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>516.8200000000001</v>
+        <v>186.92</v>
       </c>
       <c r="G193" t="n">
-        <v>466.22</v>
+        <v>181.51</v>
       </c>
       <c r="H193" t="n">
-        <v>114.53</v>
+        <v>26.48</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[1082.76, 633.17, 944.73]</t>
+          <t>[564.76, 538.1, 422.78]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[302.31, 918.78, 612.13]</t>
+          <t>[711.12, 691.74, 667.3]</t>
         </is>
       </c>
     </row>
@@ -9320,17 +9320,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9339,22 +9339,22 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>371.32</v>
+        <v>142.57</v>
       </c>
       <c r="G194" t="n">
-        <v>257.8</v>
+        <v>135.68</v>
       </c>
       <c r="H194" t="n">
-        <v>34.78</v>
+        <v>21.26</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[283.96, 565.66, 425.21]</t>
+          <t>[600.42, 472.01, 685.76]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[918.78, 612.13, 333.1]</t>
+          <t>[691.74, 667.3, 565.34]</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9381,26 +9381,26 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>659.38</v>
+        <v>306.91</v>
       </c>
       <c r="G195" t="n">
-        <v>641.5</v>
+        <v>269.7</v>
       </c>
       <c r="H195" t="n">
-        <v>177.72</v>
+        <v>37.72</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[1064.1, 1158.61, 952.93]</t>
+          <t>[502.69, 732.98, 333.76]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[612.13, 333.1, 305.92]</t>
+          <t>[667.3, 565.34, 810.6]</t>
         </is>
       </c>
     </row>
@@ -9412,41 +9412,41 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>527.86</v>
+        <v>328.52</v>
       </c>
       <c r="G196" t="n">
-        <v>523.37</v>
+        <v>312.55</v>
       </c>
       <c r="H196" t="n">
-        <v>138.26</v>
+        <v>47.67</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[926.24, 852.9, 312.41]</t>
+          <t>[971.86, 451.55, 469.56]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[333.1, 305.92, 742.4]</t>
+          <t>[565.34, 810.6, 641.64]</t>
         </is>
       </c>
     </row>
@@ -9458,41 +9458,41 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>414.15</v>
+        <v>424.45</v>
       </c>
       <c r="G197" t="n">
-        <v>395.35</v>
+        <v>419.92</v>
       </c>
       <c r="H197" t="n">
-        <v>72.75</v>
+        <v>55.68</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[596.6, 173.85, 373.78]</t>
+          <t>[318.42, 300.59, 375.77]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[305.92, 742.4, 700.6]</t>
+          <t>[810.6, 641.64, 802.3]</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9523,22 +9523,22 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>569.46</v>
+        <v>152.33</v>
       </c>
       <c r="G198" t="n">
-        <v>565.71</v>
+        <v>146.31</v>
       </c>
       <c r="H198" t="n">
-        <v>78.61</v>
+        <v>20.62</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[85.29, 191.63, 180.08]</t>
+          <t>[459.65, 715.55, 920.27]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[742.4, 700.6, 711.12]</t>
+          <t>[641.64, 802.3, 750.07]</t>
         </is>
       </c>
     </row>
@@ -9550,17 +9550,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9569,22 +9569,22 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>184.52</v>
+        <v>191.13</v>
       </c>
       <c r="G199" t="n">
-        <v>182.62</v>
+        <v>158.24</v>
       </c>
       <c r="H199" t="n">
-        <v>26.06</v>
+        <v>20.89</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[554.65, 516.08, 484.87]</t>
+          <t>[737.99, 1058.33, 652.15]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[700.6, 711.12, 691.74]</t>
+          <t>[802.3, 750.07, 754.31]</t>
         </is>
       </c>
     </row>
@@ -9596,17 +9596,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9615,22 +9615,22 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>186.92</v>
+        <v>276.34</v>
       </c>
       <c r="G200" t="n">
-        <v>181.51</v>
+        <v>249.14</v>
       </c>
       <c r="H200" t="n">
-        <v>26.48</v>
+        <v>30.52</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[564.76, 538.1, 422.78]</t>
+          <t>[1098.55, 673.31, 607.73]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[711.12, 691.74, 667.3]</t>
+          <t>[750.07, 754.31, 925.67]</t>
         </is>
       </c>
     </row>
@@ -9642,17 +9642,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -9661,22 +9661,22 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>142.57</v>
+        <v>350.89</v>
       </c>
       <c r="G201" t="n">
-        <v>135.68</v>
+        <v>335.78</v>
       </c>
       <c r="H201" t="n">
-        <v>21.26</v>
+        <v>44.8</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[600.42, 472.01, 685.76]</t>
+          <t>[562.58, 516.87, 220.8]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[691.74, 667.3, 565.34]</t>
+          <t>[754.31, 925.67, 627.6]</t>
         </is>
       </c>
     </row>
